--- a/Assets/Resources/Configs/Excel/RoleConfig.xlsx
+++ b/Assets/Resources/Configs/Excel/RoleConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123">
   <si>
     <t>id</t>
   </si>
@@ -52,6 +52,9 @@
     <t>攻击距离</t>
   </si>
   <si>
+    <t>攻击速度</t>
+  </si>
+  <si>
     <t>#RoleInfo</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t>attackDic</t>
+  </si>
+  <si>
+    <t>attackSpeed</t>
   </si>
   <si>
     <t>int</t>
@@ -781,16 +787,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="5" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="22.625" customWidth="1"/>
     <col min="7" max="8" width="10.375" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="14" max="14" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:14">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -827,92 +835,101 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -921,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -944,13 +961,16 @@
       <c r="M4">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="5" spans="2:13">
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -959,10 +979,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <v>100</v>
@@ -982,13 +1002,16 @@
       <c r="M5">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="6" spans="2:13">
+      <c r="N5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -997,10 +1020,10 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H6">
         <v>100</v>
@@ -1020,13 +1043,16 @@
       <c r="M6">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="7" spans="2:13">
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1035,10 +1061,10 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -1058,13 +1084,16 @@
       <c r="M7">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="8" spans="2:13">
+      <c r="N7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1073,10 +1102,10 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -1096,13 +1125,16 @@
       <c r="M8">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="9" spans="2:13">
+      <c r="N8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1111,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -1134,13 +1166,16 @@
       <c r="M9">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="10" spans="2:13">
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1149,10 +1184,10 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -1172,13 +1207,16 @@
       <c r="M10">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="11" spans="2:13">
+      <c r="N10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -1187,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -1210,13 +1248,16 @@
       <c r="M11">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="12" spans="2:13">
+      <c r="N11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1225,10 +1266,10 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -1248,13 +1289,16 @@
       <c r="M12">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="13" spans="2:13">
+      <c r="N12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
       <c r="B13">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1263,10 +1307,10 @@
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H13">
         <v>100</v>
@@ -1286,13 +1330,16 @@
       <c r="M13">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="14" spans="2:13">
+      <c r="N13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -1301,10 +1348,10 @@
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H14">
         <v>100</v>
@@ -1324,13 +1371,16 @@
       <c r="M14">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="15" spans="2:13">
+      <c r="N14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1339,10 +1389,10 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H15">
         <v>100</v>
@@ -1362,13 +1412,16 @@
       <c r="M15">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="16" spans="2:13">
+      <c r="N15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
       <c r="B16">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1377,10 +1430,10 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -1400,13 +1453,16 @@
       <c r="M16">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="17" spans="2:13">
+      <c r="N16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17">
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1415,10 +1471,10 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H17">
         <v>100</v>
@@ -1438,13 +1494,16 @@
       <c r="M17">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="18" spans="2:13">
+      <c r="N17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
       <c r="B18">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1453,10 +1512,10 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -1476,13 +1535,16 @@
       <c r="M18">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="19" spans="2:13">
+      <c r="N18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
       <c r="B19">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1491,10 +1553,10 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19">
         <v>100</v>
@@ -1514,13 +1576,16 @@
       <c r="M19">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="20" spans="2:13">
+      <c r="N19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
       <c r="B20">
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1529,10 +1594,10 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H20">
         <v>100</v>
@@ -1552,13 +1617,16 @@
       <c r="M20">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="21" spans="2:13">
+      <c r="N20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
       <c r="B21">
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1567,10 +1635,10 @@
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H21">
         <v>100</v>
@@ -1590,13 +1658,16 @@
       <c r="M21">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="22" spans="2:13">
+      <c r="N21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22">
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1605,10 +1676,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H22">
         <v>100</v>
@@ -1628,13 +1699,16 @@
       <c r="M22">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="23" spans="2:13">
+      <c r="N22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
       <c r="B23">
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1643,10 +1717,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H23">
         <v>100</v>
@@ -1666,13 +1740,16 @@
       <c r="M23">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="24" spans="2:13">
+      <c r="N23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
       <c r="B24">
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1681,10 +1758,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H24">
         <v>100</v>
@@ -1704,13 +1781,16 @@
       <c r="M24">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="25" spans="2:13">
+      <c r="N24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
       <c r="B25">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1719,10 +1799,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H25">
         <v>100</v>
@@ -1742,13 +1822,16 @@
       <c r="M25">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="26" spans="2:13">
+      <c r="N25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
       <c r="B26">
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -1757,10 +1840,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H26">
         <v>100</v>
@@ -1780,13 +1863,16 @@
       <c r="M26">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="27" spans="2:13">
+      <c r="N26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
       <c r="B27">
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1795,10 +1881,10 @@
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H27">
         <v>100</v>
@@ -1818,13 +1904,16 @@
       <c r="M27">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="28" spans="2:13">
+      <c r="N27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
       <c r="B28">
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1833,10 +1922,10 @@
         <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H28">
         <v>100</v>
@@ -1856,13 +1945,16 @@
       <c r="M28">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="29" spans="2:13">
+      <c r="N28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
       <c r="B29">
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1871,10 +1963,10 @@
         <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H29">
         <v>100</v>
@@ -1894,13 +1986,16 @@
       <c r="M29">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="30" spans="2:13">
+      <c r="N29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
       <c r="B30">
         <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1909,10 +2004,10 @@
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H30">
         <v>100</v>
@@ -1932,13 +2027,16 @@
       <c r="M30">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="31" spans="2:13">
+      <c r="N30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
       <c r="B31">
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1947,10 +2045,10 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H31">
         <v>100</v>
@@ -1970,13 +2068,16 @@
       <c r="M31">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:13">
+      <c r="N31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
       <c r="B32">
         <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1985,10 +2086,10 @@
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H32">
         <v>100</v>
@@ -2008,13 +2109,16 @@
       <c r="M32">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="33" spans="2:13">
+      <c r="N32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
       <c r="B33">
         <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2023,10 +2127,10 @@
         <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H33">
         <v>100</v>
@@ -2046,13 +2150,16 @@
       <c r="M33">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="34" spans="2:13">
+      <c r="N33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
       <c r="B34">
         <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -2061,10 +2168,10 @@
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -2083,6 +2190,9 @@
       </c>
       <c r="M34">
         <v>4.5</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Configs/Excel/RoleConfig.xlsx
+++ b/Assets/Resources/Configs/Excel/RoleConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15600" windowHeight="6780"/>
+    <workbookView windowWidth="28680" windowHeight="12620"/>
   </bookViews>
   <sheets>
     <sheet name="Role" sheetId="1" r:id="rId1"/>
@@ -959,7 +959,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -1041,7 +1041,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1082,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="M8">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="M9">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -1205,7 +1205,7 @@
         <v>2</v>
       </c>
       <c r="M10">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N10">
         <v>1</v>
@@ -1246,7 +1246,7 @@
         <v>2</v>
       </c>
       <c r="M11">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -1287,7 +1287,7 @@
         <v>2</v>
       </c>
       <c r="M12">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -1328,7 +1328,7 @@
         <v>2</v>
       </c>
       <c r="M13">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -1369,7 +1369,7 @@
         <v>2</v>
       </c>
       <c r="M14">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -1410,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="M15">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -1451,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="M16">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -1492,7 +1492,7 @@
         <v>2</v>
       </c>
       <c r="M17">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -1533,7 +1533,7 @@
         <v>2</v>
       </c>
       <c r="M18">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -1574,7 +1574,7 @@
         <v>2</v>
       </c>
       <c r="M19">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="M20">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -1656,7 +1656,7 @@
         <v>2</v>
       </c>
       <c r="M21">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N21">
         <v>1</v>
@@ -1697,7 +1697,7 @@
         <v>2</v>
       </c>
       <c r="M22">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -1738,7 +1738,7 @@
         <v>2</v>
       </c>
       <c r="M23">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -1779,7 +1779,7 @@
         <v>2</v>
       </c>
       <c r="M24">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -1820,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="M25">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -1861,7 +1861,7 @@
         <v>2</v>
       </c>
       <c r="M26">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>2</v>
       </c>
       <c r="M27">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -1943,7 +1943,7 @@
         <v>2</v>
       </c>
       <c r="M28">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N28">
         <v>1</v>
@@ -1984,7 +1984,7 @@
         <v>2</v>
       </c>
       <c r="M29">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="M30">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -2066,7 +2066,7 @@
         <v>2</v>
       </c>
       <c r="M31">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -2107,7 +2107,7 @@
         <v>2</v>
       </c>
       <c r="M32">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -2148,7 +2148,7 @@
         <v>2</v>
       </c>
       <c r="M33">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -2189,7 +2189,7 @@
         <v>2</v>
       </c>
       <c r="M34">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="N34">
         <v>1</v>
